--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="463">
   <si>
     <t>Filename</t>
   </si>
@@ -808,148 +808,151 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9792,0.0003,0.0091,0.0016</t>
-  </si>
-  <si>
-    <t>0.0118,0.0000,0.0001,0.9974</t>
-  </si>
-  <si>
-    <t>0.9700,0.0001,0.0026,0.0125</t>
-  </si>
-  <si>
-    <t>0.0454,0.0000,0.0192,0.9409</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9518,0.0005,0.0281,0.0034</t>
+  </si>
+  <si>
+    <t>0.0109,0.0000,0.0004,0.9966</t>
+  </si>
+  <si>
+    <t>0.9771,0.0001,0.0007,0.0185</t>
+  </si>
+  <si>
+    <t>0.2698,0.0001,0.0116,0.7634</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9177,0.0056,0.0486,0.0019</t>
-  </si>
-  <si>
-    <t>0.0123,0.0027,0.9839,0.0003</t>
-  </si>
-  <si>
-    <t>0.6754,0.0029,0.3820,0.0003</t>
-  </si>
-  <si>
-    <t>0.1136,0.0033,0.8823,0.0011</t>
-  </si>
-  <si>
-    <t>0.7233,0.0034,0.2469,0.0070</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.9866,0.0054,0.0000</t>
-  </si>
-  <si>
-    <t>0.0135,0.9790,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.0372,0.9708,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.6519,0.0022,0.4068,0.0012</t>
-  </si>
-  <si>
-    <t>0.8129,0.0028,0.2026,0.0019</t>
-  </si>
-  <si>
-    <t>0.0237,0.0014,0.9757,0.0004</t>
-  </si>
-  <si>
-    <t>0.2593,0.0032,0.7507,0.0010</t>
-  </si>
-  <si>
-    <t>0.5826,0.0010,0.4920,0.0005</t>
-  </si>
-  <si>
-    <t>0.0277,0.0014,0.9745,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.9076,0.0885,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.8263,0.0254,0.1113,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0120,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0194,0.9631,0.0212,0.0001</t>
-  </si>
-  <si>
-    <t>0.9919,0.0007,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.8967,0.0030,0.0742,0.0015</t>
-  </si>
-  <si>
-    <t>0.9295,0.1027,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0077,0.9591,0.1366,0.0001</t>
-  </si>
-  <si>
-    <t>0.0044,0.9260,0.2468,0.0016</t>
-  </si>
-  <si>
-    <t>0.2601,0.0196,0.6779,0.0064</t>
-  </si>
-  <si>
-    <t>0.0025,0.0885,0.9920,0.0000</t>
-  </si>
-  <si>
-    <t>0.0148,0.0006,0.9825,0.0007</t>
-  </si>
-  <si>
-    <t>0.0600,0.0196,0.9269,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0520,0.9927,0.0000</t>
-  </si>
-  <si>
-    <t>0.1582,0.0045,0.0157,0.8301</t>
-  </si>
-  <si>
-    <t>0.0320,0.9760,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0018,0.9954,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.0094,0.9913,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.4567,0.9857,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.6278,0.9482,0.0000</t>
-  </si>
-  <si>
-    <t>0.1212,0.0017,0.9008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0194,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0092,0.1247,0.9647,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
+    <t>0.7801,0.0051,0.2190,0.0042</t>
+  </si>
+  <si>
+    <t>0.0255,0.0017,0.9734,0.0005</t>
+  </si>
+  <si>
+    <t>0.3207,0.0045,0.7031,0.0005</t>
+  </si>
+  <si>
+    <t>0.2450,0.0038,0.7593,0.0017</t>
+  </si>
+  <si>
+    <t>0.9132,0.0019,0.0740,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.9980,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9943,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.1218,0.8905,0.0069,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.9943,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.7825,0.0019,0.2023,0.0052</t>
+  </si>
+  <si>
+    <t>0.7357,0.0051,0.2814,0.0017</t>
+  </si>
+  <si>
+    <t>0.0110,0.0017,0.9878,0.0001</t>
+  </si>
+  <si>
+    <t>0.5794,0.0063,0.4237,0.0009</t>
+  </si>
+  <si>
+    <t>0.1791,0.0023,0.8392,0.0005</t>
+  </si>
+  <si>
+    <t>0.0185,0.0025,0.9801,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9423,0.0326,0.0095,0.0003</t>
+  </si>
+  <si>
+    <t>0.9378,0.0053,0.0257,0.0035</t>
+  </si>
+  <si>
+    <t>0.0000,0.0128,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1619,0.6633,0.0826,0.0002</t>
+  </si>
+  <si>
+    <t>0.9913,0.0010,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.1163,0.0210,0.8346,0.0017</t>
+  </si>
+  <si>
+    <t>0.7389,0.3727,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.9775,0.0297,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.7302,0.9624,0.0001</t>
+  </si>
+  <si>
+    <t>0.1243,0.0375,0.8207,0.0038</t>
+  </si>
+  <si>
+    <t>0.0072,0.0235,0.9864,0.0002</t>
+  </si>
+  <si>
+    <t>0.3279,0.0019,0.6626,0.0053</t>
+  </si>
+  <si>
+    <t>0.0511,0.0768,0.8907,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9911,0.1082,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.1123,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.3960,0.0024,0.0499,0.4997</t>
+  </si>
+  <si>
+    <t>0.0075,0.9926,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0096,0.9846,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.9990,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.1760,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9684,0.9757,0.0000</t>
+  </si>
+  <si>
+    <t>0.1710,0.0021,0.8669,0.0001</t>
+  </si>
+  <si>
+    <t>0.0064,0.0007,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0340,0.0037,0.9674,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0109,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
@@ -958,448 +961,448 @@
     <t>0.9993,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0595,0.9998,0.0000</t>
+    <t>0.0000,0.0147,0.9999,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9968,0.8821,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0165,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0701,0.0057,0.9128,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0036,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0073,0.9909,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.9983,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3100,0.0048,0.7288,0.0003</t>
-  </si>
-  <si>
-    <t>0.7577,0.1154,0.0850,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0044,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9923,0.9841,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9832,0.4452,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9962,0.0233,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9753,0.5827,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.0000,0.0030,0.9946</t>
+    <t>0.0000,0.9984,0.9370,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0130,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0118,0.2601,0.9286,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9938,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0049,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0080,0.9915,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9992,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2271,0.0104,0.7713,0.0002</t>
+  </si>
+  <si>
+    <t>0.8414,0.0343,0.0961,0.0022</t>
+  </si>
+  <si>
+    <t>0.0000,0.0083,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9635,0.9648,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9904,0.1655,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9958,0.0137,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9587,0.0000</t>
+  </si>
+  <si>
+    <t>0.1234,0.0001,0.0101,0.8709</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0063,0.0000,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0107,0.0000,0.0000,0.9982</t>
   </si>
   <si>
     <t>0.0006,0.0000,0.0000,0.9998</t>
   </si>
   <si>
-    <t>0.0006,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0005,0.9993</t>
-  </si>
-  <si>
-    <t>0.0096,0.0000,0.0000,0.9982</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0014,0.9632,0.5644,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9743,0.9176,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9465,0.9591,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9593,0.7179,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.8051,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9893,0.8176,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0929,0.0078,0.9105,0.0002</t>
-  </si>
-  <si>
-    <t>0.9633,0.0026,0.0149,0.0012</t>
-  </si>
-  <si>
-    <t>0.0115,0.0015,0.9866,0.0002</t>
-  </si>
-  <si>
-    <t>0.0515,0.9627,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9974,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.1091,0.9336,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.1272,0.9280,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9977,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9989,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8520,0.2373,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.6929,0.0027,0.2771,0.0058</t>
-  </si>
-  <si>
-    <t>0.9321,0.0032,0.0486,0.0004</t>
-  </si>
-  <si>
-    <t>0.8017,0.0139,0.1243,0.0043</t>
-  </si>
-  <si>
-    <t>0.7888,0.0049,0.1511,0.0121</t>
-  </si>
-  <si>
-    <t>0.0476,0.0022,0.0028,0.9624</t>
-  </si>
-  <si>
-    <t>0.0042,0.9936,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9974,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9902,0.0181,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9901,0.9884,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.9905,0.0061,0.0000</t>
-  </si>
-  <si>
-    <t>0.9029,0.1365,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0084,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.4867,0.9784,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.6113,0.9608,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0721,0.9864,0.0001</t>
-  </si>
-  <si>
-    <t>0.0092,0.0168,0.9814,0.0002</t>
-  </si>
-  <si>
-    <t>0.7935,0.0017,0.1476,0.0159</t>
-  </si>
-  <si>
-    <t>0.4240,0.0034,0.5775,0.0047</t>
-  </si>
-  <si>
-    <t>0.0416,0.0009,0.9626,0.0006</t>
-  </si>
-  <si>
-    <t>0.8740,0.0182,0.0552,0.0023</t>
-  </si>
-  <si>
-    <t>0.1235,0.0000,0.0001,0.9735</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0025,0.0000,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9831,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.7629,0.3345,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9388,0.0847,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.5486,0.0001,0.0071,0.4984</t>
-  </si>
-  <si>
-    <t>0.0003,0.1048,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.9691,0.0000,0.0035,0.0142</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.6703,0.2690,0.0372,0.0010</t>
-  </si>
-  <si>
-    <t>0.9640,0.0018,0.0109,0.0038</t>
-  </si>
-  <si>
-    <t>0.9707,0.0040,0.0120,0.0008</t>
-  </si>
-  <si>
-    <t>0.6681,0.2229,0.0308,0.0046</t>
-  </si>
-  <si>
-    <t>0.7301,0.0456,0.1769,0.0013</t>
-  </si>
-  <si>
-    <t>0.9143,0.0170,0.0409,0.0015</t>
+    <t>0.0002,0.9933,0.5405,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9911,0.9721,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9931,0.9262,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9360,0.9566,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9564,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9889,0.8534,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.1088,0.0028,0.9028,0.0002</t>
+  </si>
+  <si>
+    <t>0.9729,0.0005,0.0186,0.0004</t>
+  </si>
+  <si>
+    <t>0.0656,0.0016,0.9416,0.0004</t>
+  </si>
+  <si>
+    <t>0.0332,0.9772,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9977,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0880,0.9448,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.3629,0.7712,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.9933,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9990,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8217,0.3126,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.7552,0.0020,0.2273,0.0067</t>
+  </si>
+  <si>
+    <t>0.8995,0.0030,0.0936,0.0005</t>
+  </si>
+  <si>
+    <t>0.7758,0.0172,0.1625,0.0023</t>
+  </si>
+  <si>
+    <t>0.4888,0.0040,0.4238,0.0238</t>
+  </si>
+  <si>
+    <t>0.1346,0.0011,0.0026,0.8970</t>
+  </si>
+  <si>
+    <t>0.0573,0.9570,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9976,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9914,0.0482,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9813,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.9906,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.9395,0.0654,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.9849,0.0222,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.7168,0.9352,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.8502,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0492,0.9927,0.0000</t>
+  </si>
+  <si>
+    <t>0.0217,0.1039,0.9356,0.0001</t>
+  </si>
+  <si>
+    <t>0.9093,0.0024,0.0651,0.0025</t>
+  </si>
+  <si>
+    <t>0.6451,0.0062,0.3231,0.0064</t>
+  </si>
+  <si>
+    <t>0.2627,0.0006,0.7787,0.0011</t>
+  </si>
+  <si>
+    <t>0.8427,0.0101,0.1211,0.0035</t>
+  </si>
+  <si>
+    <t>0.0264,0.0000,0.0002,0.9938</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0034,0.0000,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,0.9785,0.9735,0.0000</t>
+  </si>
+  <si>
+    <t>0.8331,0.2401,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.8774,0.1551,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.3588,0.0001,0.0014,0.8166</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0246,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9859,0.0001,0.0034,0.0047</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.4815,0.4368,0.0445,0.0012</t>
+  </si>
+  <si>
+    <t>0.9450,0.0110,0.0201,0.0013</t>
+  </si>
+  <si>
+    <t>0.9764,0.0022,0.0083,0.0015</t>
+  </si>
+  <si>
+    <t>0.6831,0.1532,0.0491,0.0052</t>
+  </si>
+  <si>
+    <t>0.8537,0.0116,0.1154,0.0010</t>
+  </si>
+  <si>
+    <t>0.9186,0.0255,0.0266,0.0011</t>
+  </si>
+  <si>
+    <t>0.9780,0.0248,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9097,0.1246,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.9115,0.1639,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.4006,0.0288,0.4879,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0051,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9934,0.0046,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9921,0.0055,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0065,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9876,0.0073,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0025,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0063,0.0130,0.9890,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0011,0.9972,0.0005</t>
+  </si>
+  <si>
+    <t>0.0048,0.0332,0.9845,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0093,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0057,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.2387,0.0027,0.7477,0.0042</t>
+  </si>
+  <si>
+    <t>0.0468,0.0055,0.9461,0.0006</t>
+  </si>
+  <si>
+    <t>0.3401,0.0048,0.6021,0.0224</t>
+  </si>
+  <si>
+    <t>0.4520,0.0168,0.5075,0.0009</t>
+  </si>
+  <si>
+    <t>0.4224,0.2729,0.1294,0.0040</t>
+  </si>
+  <si>
+    <t>0.8370,0.0114,0.1367,0.0008</t>
+  </si>
+  <si>
+    <t>0.6831,0.0056,0.2459,0.0196</t>
+  </si>
+  <si>
+    <t>0.3982,0.0115,0.5737,0.0034</t>
+  </si>
+  <si>
+    <t>0.9261,0.1601,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7467,0.4136,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0044,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0030,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9255,0.0239,0.0151,0.0004</t>
+  </si>
+  <si>
+    <t>0.9531,0.0016,0.0375,0.0006</t>
+  </si>
+  <si>
+    <t>0.7153,0.0024,0.2497,0.0120</t>
+  </si>
+  <si>
+    <t>0.8558,0.0081,0.1115,0.0022</t>
+  </si>
+  <si>
+    <t>0.4435,0.0026,0.5747,0.0040</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0046,0.3361,0.9641,0.0002</t>
+  </si>
+  <si>
+    <t>0.0548,0.1036,0.8612,0.0002</t>
+  </si>
+  <si>
+    <t>0.0718,0.0196,0.9105,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.5237,0.9721,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9692,0.0354,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9739,0.0298,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9029,0.1678,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.1556,0.0144,0.8094,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0035,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0013,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0167,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0036,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.1634,0.9802,0.0000</t>
-  </si>
-  <si>
-    <t>0.0112,0.0014,0.9863,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.0411,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0109,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0057,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.3764,0.0066,0.6287,0.0018</t>
-  </si>
-  <si>
-    <t>0.0148,0.0024,0.9823,0.0002</t>
-  </si>
-  <si>
-    <t>0.1634,0.0073,0.8092,0.0085</t>
-  </si>
-  <si>
-    <t>0.6261,0.0538,0.2707,0.0013</t>
-  </si>
-  <si>
-    <t>0.2791,0.0904,0.4992,0.0006</t>
-  </si>
-  <si>
-    <t>0.7683,0.0185,0.1910,0.0013</t>
-  </si>
-  <si>
-    <t>0.9123,0.0036,0.0368,0.0063</t>
-  </si>
-  <si>
-    <t>0.0503,0.0108,0.9343,0.0009</t>
-  </si>
-  <si>
-    <t>0.9704,0.0604,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7833,0.3800,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0070,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0050,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9103,0.0320,0.0194,0.0006</t>
-  </si>
-  <si>
-    <t>0.9453,0.0033,0.0371,0.0004</t>
-  </si>
-  <si>
-    <t>0.8750,0.0017,0.0828,0.0071</t>
-  </si>
-  <si>
-    <t>0.7141,0.0304,0.2102,0.0028</t>
-  </si>
-  <si>
-    <t>0.2299,0.0030,0.6843,0.0271</t>
-  </si>
-  <si>
-    <t>0.0010,0.0016,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0126,0.3903,0.8844,0.0003</t>
-  </si>
-  <si>
-    <t>0.0572,0.3324,0.7061,0.0003</t>
-  </si>
-  <si>
-    <t>0.4869,0.0081,0.5395,0.0006</t>
-  </si>
-  <si>
-    <t>0.0111,0.1143,0.9511,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.0213,0.9880,0.0003</t>
-  </si>
-  <si>
-    <t>0.0926,0.2940,0.5501,0.0008</t>
-  </si>
-  <si>
-    <t>0.5909,0.0009,0.3332,0.0101</t>
-  </si>
-  <si>
-    <t>0.0010,0.0770,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6763,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.0362,0.9869,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0050,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0433,0.0061,0.9477,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0065,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0165,0.0100,0.9675,0.0009</t>
-  </si>
-  <si>
-    <t>0.0101,0.0122,0.9813,0.0003</t>
-  </si>
-  <si>
-    <t>0.2860,0.0020,0.7432,0.0017</t>
-  </si>
-  <si>
-    <t>0.3478,0.0024,0.6692,0.0030</t>
-  </si>
-  <si>
-    <t>0.4073,0.0014,0.6308,0.0028</t>
-  </si>
-  <si>
-    <t>0.1486,0.0920,0.6925,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.0204,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0354,0.9914,0.0001</t>
-  </si>
-  <si>
-    <t>0.0410,0.0185,0.9269,0.0008</t>
-  </si>
-  <si>
-    <t>0.0039,0.0079,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.1418,0.0010,0.8459,0.0030</t>
-  </si>
-  <si>
-    <t>0.1880,0.0019,0.7889,0.0045</t>
-  </si>
-  <si>
-    <t>0.0171,0.0055,0.9744,0.0007</t>
-  </si>
-  <si>
-    <t>0.6958,0.0000,0.0026,0.3775</t>
-  </si>
-  <si>
-    <t>0.0060,0.0001,0.0001,0.9980</t>
-  </si>
-  <si>
-    <t>0.0097,0.0000,0.0004,0.9969</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9880,0.0005,0.0017,0.0034</t>
+    <t>0.0020,0.0466,0.9937,0.0002</t>
+  </si>
+  <si>
+    <t>0.1971,0.0964,0.5844,0.0023</t>
+  </si>
+  <si>
+    <t>0.6080,0.0008,0.2788,0.0201</t>
+  </si>
+  <si>
+    <t>0.0033,0.0150,0.9938,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1282,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.5216,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0037,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0035,0.9915,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.1127,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0098,0.0131,0.9769,0.0005</t>
+  </si>
+  <si>
+    <t>0.0055,0.0219,0.9848,0.0002</t>
+  </si>
+  <si>
+    <t>0.3925,0.0009,0.6109,0.0071</t>
+  </si>
+  <si>
+    <t>0.2507,0.0014,0.7650,0.0019</t>
+  </si>
+  <si>
+    <t>0.8677,0.0016,0.0985,0.0066</t>
+  </si>
+  <si>
+    <t>0.1124,0.0454,0.7986,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.0183,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0087,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.1582,0.0135,0.7951,0.0010</t>
+  </si>
+  <si>
+    <t>0.0015,0.0045,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.2541,0.0005,0.7567,0.0025</t>
+  </si>
+  <si>
+    <t>0.5123,0.0017,0.4935,0.0031</t>
+  </si>
+  <si>
+    <t>0.0123,0.0054,0.9805,0.0005</t>
+  </si>
+  <si>
+    <t>0.9117,0.0000,0.0071,0.0402</t>
+  </si>
+  <si>
+    <t>0.0461,0.0005,0.0025,0.9714</t>
+  </si>
+  <si>
+    <t>0.0767,0.0000,0.0011,0.9694</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.7637,0.0004,0.0041,0.2570</t>
   </si>
 </sst>
 </file>
@@ -1785,7 +1788,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1799,7 +1802,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1813,7 +1816,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1827,7 +1830,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1841,7 +1844,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1855,7 +1858,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1869,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1883,7 +1886,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1897,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1911,7 +1914,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1925,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1939,7 +1942,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1953,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1967,7 +1970,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1978,10 +1981,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1995,7 +1998,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2009,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2023,7 +2026,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2037,7 +2040,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2051,7 +2054,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2065,7 +2068,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2079,7 +2082,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2093,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2107,7 +2110,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2121,7 +2124,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2132,10 +2135,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2146,10 +2149,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2163,7 +2166,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2177,7 +2180,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2191,7 +2194,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2205,7 +2208,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2219,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2233,7 +2236,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2247,7 +2250,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2258,10 +2261,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2275,7 +2278,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2289,7 +2292,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2300,10 +2303,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2317,7 +2320,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2331,7 +2334,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2345,7 +2348,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2359,7 +2362,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2373,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2387,7 +2390,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2398,10 +2401,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2415,7 +2418,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2429,7 +2432,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2443,7 +2446,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2457,7 +2460,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2471,7 +2474,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2485,7 +2488,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2499,7 +2502,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2513,7 +2516,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2527,7 +2530,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2541,7 +2544,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2555,7 +2558,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2569,7 +2572,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2583,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2597,7 +2600,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2611,7 +2614,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2625,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2639,7 +2642,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2653,7 +2656,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2667,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2681,7 +2684,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2695,7 +2698,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2709,7 +2712,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2723,7 +2726,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2737,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2751,7 +2754,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2765,7 +2768,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2779,7 +2782,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2793,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2807,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2821,7 +2824,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2835,7 +2838,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2849,7 +2852,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2863,7 +2866,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2877,7 +2880,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2891,7 +2894,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2905,7 +2908,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2919,7 +2922,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2933,7 +2936,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2947,7 +2950,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2961,7 +2964,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2975,7 +2978,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2989,7 +2992,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3003,7 +3006,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3017,7 +3020,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3031,7 +3034,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3045,7 +3048,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3059,7 +3062,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3073,7 +3076,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3087,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3101,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3115,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3129,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3143,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3157,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3171,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3185,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3199,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3213,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3227,7 +3230,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3241,7 +3244,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3255,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3269,7 +3272,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3283,7 +3286,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3297,7 +3300,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3311,7 +3314,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3325,7 +3328,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3339,7 +3342,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3353,7 +3356,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3367,7 +3370,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3381,7 +3384,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3395,7 +3398,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3409,7 +3412,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3420,10 +3423,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3437,7 +3440,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3451,7 +3454,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3465,7 +3468,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3479,7 +3482,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3493,7 +3496,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3507,7 +3510,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3521,7 +3524,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3535,7 +3538,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3549,7 +3552,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3563,7 +3566,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3577,7 +3580,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3591,7 +3594,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3605,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3619,7 +3622,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3633,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3647,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3658,10 +3661,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3675,7 +3678,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3689,7 +3692,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3703,7 +3706,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3717,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3728,10 +3731,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3745,7 +3748,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3759,7 +3762,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3773,7 +3776,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3787,7 +3790,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3801,7 +3804,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3815,7 +3818,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3829,7 +3832,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3843,7 +3846,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3857,7 +3860,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3871,7 +3874,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3885,7 +3888,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3899,7 +3902,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3910,10 +3913,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3927,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>312</v>
+        <v>385</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3941,7 +3944,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3955,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3969,7 +3972,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3980,10 +3983,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3997,7 +4000,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4011,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4025,7 +4028,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4039,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4053,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4067,7 +4070,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4081,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4095,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4109,7 +4112,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4123,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4137,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>393</v>
+        <v>313</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4151,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4165,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4179,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4193,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4207,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4218,10 +4221,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4235,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4249,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4263,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>393</v>
+        <v>313</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4277,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4291,7 +4294,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4305,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4319,7 +4322,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4333,7 +4336,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4347,7 +4350,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4361,7 +4364,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4375,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4389,7 +4392,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4403,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4417,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4431,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4445,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4456,10 +4459,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4470,10 +4473,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4487,7 +4490,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4501,7 +4504,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4515,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4529,7 +4532,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4543,7 +4546,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4557,7 +4560,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4571,7 +4574,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4585,7 +4588,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4599,7 +4602,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4613,7 +4616,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4627,7 +4630,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4641,7 +4644,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4655,7 +4658,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4669,7 +4672,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4683,7 +4686,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4697,7 +4700,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4711,7 +4714,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4722,10 +4725,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4739,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4753,7 +4756,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4767,7 +4770,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4781,7 +4784,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4795,7 +4798,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4809,7 +4812,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4823,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4837,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4851,7 +4854,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4865,7 +4868,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4879,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4893,7 +4896,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4904,10 +4907,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4918,10 +4921,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4935,7 +4938,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4949,7 +4952,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4963,7 +4966,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4977,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4991,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5005,7 +5008,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5019,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5030,10 +5033,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5047,7 +5050,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5061,7 +5064,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5075,7 +5078,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5089,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>393</v>
+        <v>269</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5103,7 +5106,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>315</v>
+        <v>434</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5117,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5131,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5145,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5159,7 +5162,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5173,7 +5176,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5187,7 +5190,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5201,7 +5204,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5215,7 +5218,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5229,7 +5232,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5240,10 +5243,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5257,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5271,7 +5274,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5285,7 +5288,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5299,7 +5302,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5313,7 +5316,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5327,7 +5330,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5341,7 +5344,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
